--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113499127</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>113499128</v>
       </c>
       <c r="B5" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>113499118</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>113499120</v>
       </c>
       <c r="B7" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>115486077</v>
       </c>
       <c r="B12" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>115486075</v>
       </c>
       <c r="B13" t="n">
-        <v>57265</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>113499127</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>113499128</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>113499118</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>113499120</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>115486077</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>115486075</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1967,6 +1967,104 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>113499132</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92535</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3382</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Aspskinn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Conferticium ravum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Burt) Ginns &amp; G.W. Freeman</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>570262</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6697746</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -1972,7 +1972,7 @@
         <v>113499132</v>
       </c>
       <c r="B14" t="n">
-        <v>92535</v>
+        <v>92543</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -1972,7 +1972,7 @@
         <v>113499132</v>
       </c>
       <c r="B14" t="n">
-        <v>92543</v>
+        <v>92635</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -1972,7 +1972,7 @@
         <v>113499132</v>
       </c>
       <c r="B14" t="n">
-        <v>92635</v>
+        <v>92647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -1972,7 +1972,7 @@
         <v>113499132</v>
       </c>
       <c r="B14" t="n">
-        <v>92647</v>
+        <v>92649</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -1972,7 +1972,7 @@
         <v>113499132</v>
       </c>
       <c r="B14" t="n">
-        <v>92649</v>
+        <v>92650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -1972,7 +1972,7 @@
         <v>113499132</v>
       </c>
       <c r="B14" t="n">
-        <v>92650</v>
+        <v>92677</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113499114</v>
+        <v>113499113</v>
       </c>
       <c r="B2" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570171</v>
+        <v>570282</v>
       </c>
       <c r="R2" t="n">
-        <v>6698149</v>
+        <v>6697979</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113499127</v>
+        <v>113499114</v>
       </c>
       <c r="B3" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570138</v>
+        <v>570171</v>
       </c>
       <c r="R3" t="n">
-        <v>6698090</v>
+        <v>6698149</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -861,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-12-03</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113499113</v>
+        <v>113499132</v>
       </c>
       <c r="B4" t="n">
-        <v>90332</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -908,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>3382</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Conferticium ravum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Burt) Ginns &amp; G.W. Freeman</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570282</v>
+        <v>570262</v>
       </c>
       <c r="R4" t="n">
-        <v>6697979</v>
+        <v>6697746</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,6 +948,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -994,15 +967,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113499128</v>
+        <v>118927162</v>
       </c>
       <c r="B5" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1010,45 +978,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4404</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spjutbo, Dlr</t>
+          <t>Kalven, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>570132</v>
+        <v>570190</v>
       </c>
       <c r="R5" t="n">
-        <v>6698077</v>
+        <v>6698184</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,17 +1032,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,15 +1064,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113499118</v>
+        <v>118927163</v>
       </c>
       <c r="B6" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,37 +1075,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4404</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spjutbo, Dlr</t>
+          <t>Kalven, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>570246</v>
+        <v>570185</v>
       </c>
       <c r="R6" t="n">
-        <v>6698037</v>
+        <v>6698132</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,17 +1129,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Spår av barkfläkning</t>
+          <t>2024-08-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1216,32 +1161,27 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113499120</v>
+        <v>115486080</v>
       </c>
       <c r="B7" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1250,16 +1190,24 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spjutbo, Dlr</t>
+          <t>Södra Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>570229</v>
+        <v>570160</v>
       </c>
       <c r="R7" t="n">
-        <v>6698004</v>
+        <v>6698024</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1286,17 +1234,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spår av barkfläkning</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,15 +1266,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115486080</v>
+        <v>113499116</v>
       </c>
       <c r="B8" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1339,16 +1277,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1357,24 +1295,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Södra Spjutbo, Dlr</t>
+          <t>Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>570160</v>
+        <v>570117</v>
       </c>
       <c r="R8" t="n">
-        <v>6698024</v>
+        <v>6698034</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1401,12 +1331,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spår av barkfläkning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1433,50 +1368,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115486073</v>
+        <v>113499117</v>
       </c>
       <c r="B9" t="n">
-        <v>100812</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Södra Spjutbo, Dlr</t>
+          <t>Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>570173</v>
+        <v>570123</v>
       </c>
       <c r="R9" t="n">
-        <v>6698131</v>
+        <v>6698036</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1503,12 +1433,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Spår av barkfläkning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,50 +1470,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>115486072</v>
+        <v>113499118</v>
       </c>
       <c r="B10" t="n">
-        <v>100812</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Södra Spjutbo, Dlr</t>
+          <t>Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>570120</v>
+        <v>570246</v>
       </c>
       <c r="R10" t="n">
-        <v>6698093</v>
+        <v>6698037</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1605,12 +1535,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spår av barkfläkning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1637,50 +1572,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>115486074</v>
+        <v>113499120</v>
       </c>
       <c r="B11" t="n">
-        <v>100812</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221235</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Södra Spjutbo, Dlr</t>
+          <t>Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>570174</v>
+        <v>570229</v>
       </c>
       <c r="R11" t="n">
-        <v>6698140</v>
+        <v>6698004</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1707,12 +1637,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spår av barkfläkning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1739,15 +1674,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>115486077</v>
+        <v>113499127</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1783,11 +1713,11 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Södra Spjutbo, Dlr</t>
+          <t>Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>570141</v>
+        <v>570138</v>
       </c>
       <c r="R12" t="n">
         <v>6698090</v>
@@ -1817,17 +1747,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gammalt ringhack</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1854,15 +1784,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>115486075</v>
+        <v>113499128</v>
       </c>
       <c r="B13" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,20 +1817,20 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Södra Spjutbo, Dlr</t>
+          <t>Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>570238</v>
+        <v>570132</v>
       </c>
       <c r="R13" t="n">
-        <v>6697824</v>
+        <v>6698077</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1932,17 +1857,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2023-12-03</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Barkfläkning</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1894,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113499132</v>
+        <v>115486075</v>
       </c>
       <c r="B14" t="n">
-        <v>92687</v>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,34 +1905,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3382</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Aspskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Conferticium ravum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Burt) Ginns &amp; G.W. Freeman</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spjutbo, Dlr</t>
+          <t>Södra Spjutbo, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>570262</v>
+        <v>570238</v>
       </c>
       <c r="R14" t="n">
-        <v>6697746</v>
+        <v>6697824</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2034,12 +1967,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-12-03</t>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Barkfläkning</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2048,7 +1986,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2064,6 +2001,722 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>115486077</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>570141</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6698090</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Gammalt ringhack</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>115486079</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>570104</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6698075</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>113499121</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>570112</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6698059</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>113499123</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>570115</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6698055</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-12-03</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>115486072</v>
+      </c>
+      <c r="B19" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>570120</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6698093</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>115486073</v>
+      </c>
+      <c r="B20" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>570173</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6698131</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>115486074</v>
+      </c>
+      <c r="B21" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Södra Spjutbo, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>570174</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6698140</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Husby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-03-28</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 992-2024 artfynd.xlsx
+++ b/artfynd/A 992-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499132</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115486075</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -977,6 +992,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499113</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499114</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927162</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118927163</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1373,6 +1408,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115486080</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1475,6 +1515,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499116</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499117</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1679,6 +1729,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499118</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499120</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1891,6 +1951,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499127</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499128</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2111,6 +2181,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115486077</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2216,6 +2291,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115486079</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2321,6 +2401,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499121</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2426,6 +2511,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113499123</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2523,6 +2613,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115486072</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2620,6 +2715,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115486073</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2717,8 +2817,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115486074</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>